--- a/full/sliding_window_results_window_3.xlsx
+++ b/full/sliding_window_results_window_3.xlsx
@@ -463,13 +463,13 @@
         <v>29.35</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>28.56809871931244</v>
       </c>
       <c r="D2" t="n">
-        <v>-29.35</v>
+        <v>-0.7819012806875634</v>
       </c>
       <c r="E2" t="n">
-        <v>861.4225000000001</v>
+        <v>0.6113696127408518</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.37</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>28.56090230188462</v>
       </c>
       <c r="D3" t="n">
-        <v>-29.37</v>
+        <v>-0.8090976981153766</v>
       </c>
       <c r="E3" t="n">
-        <v>862.5969</v>
+        <v>0.6546390850956011</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.54</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>29.40648462030243</v>
       </c>
       <c r="D4" t="n">
-        <v>-29.54</v>
+        <v>-0.1335153796975703</v>
       </c>
       <c r="E4" t="n">
-        <v>872.6116</v>
+        <v>0.01782635661578637</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.55</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>30.00421754041881</v>
       </c>
       <c r="D5" t="n">
-        <v>-29.55</v>
+        <v>0.4542175404188136</v>
       </c>
       <c r="E5" t="n">
-        <v>873.2025</v>
+        <v>0.2063135740241165</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.75</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>30.08550511156546</v>
       </c>
       <c r="D6" t="n">
-        <v>-29.75</v>
+        <v>0.3355051115654604</v>
       </c>
       <c r="E6" t="n">
-        <v>885.0625</v>
+        <v>0.112563679886552</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>29.84</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>30.13760866815252</v>
       </c>
       <c r="D7" t="n">
-        <v>-29.84</v>
+        <v>0.2976086681525238</v>
       </c>
       <c r="E7" t="n">
-        <v>890.4256</v>
+        <v>0.08857091935951907</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>29.81</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>30.24145396543597</v>
       </c>
       <c r="D8" t="n">
-        <v>-29.81</v>
+        <v>0.4314539654359741</v>
       </c>
       <c r="E8" t="n">
-        <v>888.6360999999999</v>
+        <v>0.1861525242904268</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>29.92</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>30.23881880015279</v>
       </c>
       <c r="D9" t="n">
-        <v>-29.92</v>
+        <v>0.3188188001527905</v>
       </c>
       <c r="E9" t="n">
-        <v>895.2064000000001</v>
+        <v>0.101645427330865</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>29.98</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>30.3324748470579</v>
       </c>
       <c r="D10" t="n">
-        <v>-29.98</v>
+        <v>0.3524748470578949</v>
       </c>
       <c r="E10" t="n">
-        <v>898.8004000000001</v>
+        <v>0.1242385178084864</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.04</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>30.15780981532706</v>
       </c>
       <c r="D11" t="n">
-        <v>-30.04</v>
+        <v>0.1178098153270639</v>
       </c>
       <c r="E11" t="n">
-        <v>902.4015999999999</v>
+        <v>0.0138791525873969</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.21</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>30.00645248447812</v>
       </c>
       <c r="D12" t="n">
-        <v>-30.21</v>
+        <v>-0.2035475155218762</v>
       </c>
       <c r="E12" t="n">
-        <v>912.6441000000001</v>
+        <v>0.04143159107512844</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.22</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>30.11347628287443</v>
       </c>
       <c r="D13" t="n">
-        <v>-30.22</v>
+        <v>-0.1065237171255689</v>
       </c>
       <c r="E13" t="n">
-        <v>913.2483999999999</v>
+        <v>0.01134730231024821</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.38</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>29.99755940397955</v>
       </c>
       <c r="D14" t="n">
-        <v>-30.38</v>
+        <v>-0.382440596020448</v>
       </c>
       <c r="E14" t="n">
-        <v>922.9444</v>
+        <v>0.1462608094844755</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.44</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>30.02760648670544</v>
       </c>
       <c r="D15" t="n">
-        <v>-30.44</v>
+        <v>-0.412393513294564</v>
       </c>
       <c r="E15" t="n">
-        <v>926.5936</v>
+        <v>0.1700684098074337</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.48</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>30.198318076291</v>
       </c>
       <c r="D16" t="n">
-        <v>-30.48</v>
+        <v>-0.2816819237090051</v>
       </c>
       <c r="E16" t="n">
-        <v>929.0304</v>
+        <v>0.07934470614440579</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>30.69</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>30.46317541374856</v>
       </c>
       <c r="D17" t="n">
-        <v>-30.69</v>
+        <v>-0.2268245862514426</v>
       </c>
       <c r="E17" t="n">
-        <v>941.8761000000001</v>
+        <v>0.05144939292813814</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>30.75</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>30.7874844356307</v>
       </c>
       <c r="D18" t="n">
-        <v>-30.75</v>
+        <v>0.03748443563070225</v>
       </c>
       <c r="E18" t="n">
-        <v>945.5625</v>
+        <v>0.001405082914552261</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>30.94</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>31.48652885860169</v>
       </c>
       <c r="D19" t="n">
-        <v>-30.94</v>
+        <v>0.5465288586016932</v>
       </c>
       <c r="E19" t="n">
-        <v>957.2836000000001</v>
+        <v>0.2986937932844695</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>30.95</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>31.39704363937706</v>
       </c>
       <c r="D20" t="n">
-        <v>-30.95</v>
+        <v>0.4470436393770605</v>
       </c>
       <c r="E20" t="n">
-        <v>957.9024999999999</v>
+        <v>0.1998480155074873</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.02</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>31.22176637042529</v>
       </c>
       <c r="D21" t="n">
-        <v>-31.02</v>
+        <v>0.2017663704252861</v>
       </c>
       <c r="E21" t="n">
-        <v>962.2404</v>
+        <v>0.04070966823459377</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.12</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>31.20880547241887</v>
       </c>
       <c r="D22" t="n">
-        <v>-31.12</v>
+        <v>0.08880547241886561</v>
       </c>
       <c r="E22" t="n">
-        <v>968.4544000000001</v>
+        <v>0.0078864119315379</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.28</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>31.71783149681082</v>
       </c>
       <c r="D23" t="n">
-        <v>-31.28</v>
+        <v>0.4378314968108157</v>
       </c>
       <c r="E23" t="n">
-        <v>978.4384000000001</v>
+        <v>0.1916964195995993</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>31.38</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>31.67425022380877</v>
       </c>
       <c r="D24" t="n">
-        <v>-31.38</v>
+        <v>0.2942502238087705</v>
       </c>
       <c r="E24" t="n">
-        <v>984.7044</v>
+        <v>0.08658319421151155</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>31.58</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>31.80670018641877</v>
       </c>
       <c r="D25" t="n">
-        <v>-31.58</v>
+        <v>0.2267001864187677</v>
       </c>
       <c r="E25" t="n">
-        <v>997.2963999999999</v>
+        <v>0.05139297452230401</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>31.65</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>31.57236529702934</v>
       </c>
       <c r="D26" t="n">
-        <v>-31.65</v>
+        <v>-0.07763470297066277</v>
       </c>
       <c r="E26" t="n">
-        <v>1001.7225</v>
+        <v>0.006027147105343035</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>31.88</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>31.80795770925392</v>
       </c>
       <c r="D27" t="n">
-        <v>-31.88</v>
+        <v>-0.07204229074607937</v>
       </c>
       <c r="E27" t="n">
-        <v>1016.3344</v>
+        <v>0.005190091655942634</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>32.28</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>32.40764967107331</v>
       </c>
       <c r="D28" t="n">
-        <v>-32.28</v>
+        <v>0.127649671073307</v>
       </c>
       <c r="E28" t="n">
-        <v>1041.9984</v>
+        <v>0.01629443852512348</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>32.45</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>32.0779747708137</v>
       </c>
       <c r="D29" t="n">
-        <v>-32.45</v>
+        <v>-0.3720252291863062</v>
       </c>
       <c r="E29" t="n">
-        <v>1053.0025</v>
+        <v>0.1384027711511236</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>32.85</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>33.49615976197383</v>
       </c>
       <c r="D30" t="n">
-        <v>-32.85</v>
+        <v>0.6461597619738271</v>
       </c>
       <c r="E30" t="n">
-        <v>1079.1225</v>
+        <v>0.4175224379940728</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>32.9</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>32.90623986695228</v>
       </c>
       <c r="D31" t="n">
-        <v>-32.9</v>
+        <v>0.006239866952284956</v>
       </c>
       <c r="E31" t="n">
-        <v>1082.41</v>
+        <v>3.893593958221794e-05</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>33.1</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>33.22022286182911</v>
       </c>
       <c r="D32" t="n">
-        <v>-33.1</v>
+        <v>0.120222861829113</v>
       </c>
       <c r="E32" t="n">
-        <v>1095.61</v>
+        <v>0.014453536506382</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>33.4</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>33.03518120681197</v>
       </c>
       <c r="D33" t="n">
-        <v>-33.4</v>
+        <v>-0.3648187931880287</v>
       </c>
       <c r="E33" t="n">
-        <v>1115.56</v>
+        <v>0.1330927518631696</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>33.7</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>33.75397210975283</v>
       </c>
       <c r="D34" t="n">
-        <v>-33.7</v>
+        <v>0.05397210975282718</v>
       </c>
       <c r="E34" t="n">
-        <v>1135.69</v>
+        <v>0.002912988631171223</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>34.1</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>34.66480062472593</v>
       </c>
       <c r="D35" t="n">
-        <v>-34.1</v>
+        <v>0.5648006247259261</v>
       </c>
       <c r="E35" t="n">
-        <v>1162.81</v>
+        <v>0.3189997456907964</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>34.4</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>34.41753274239829</v>
       </c>
       <c r="D36" t="n">
-        <v>-34.4</v>
+        <v>0.01753274239828784</v>
       </c>
       <c r="E36" t="n">
-        <v>1183.36</v>
+        <v>0.00030739705600472</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>34.9</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>34.92800287556167</v>
       </c>
       <c r="D37" t="n">
-        <v>-34.9</v>
+        <v>0.02800287556166836</v>
       </c>
       <c r="E37" t="n">
-        <v>1218.01</v>
+        <v>0.0007841610397222831</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>35.3</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>34.47907648458726</v>
       </c>
       <c r="D38" t="n">
-        <v>-35.3</v>
+        <v>-0.820923515412737</v>
       </c>
       <c r="E38" t="n">
-        <v>1246.09</v>
+        <v>0.6739154181576062</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>35.7</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>34.76454817958464</v>
       </c>
       <c r="D39" t="n">
-        <v>-35.7</v>
+        <v>-0.9354518204153663</v>
       </c>
       <c r="E39" t="n">
-        <v>1274.49</v>
+        <v>0.8750701083184228</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>36.3</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>35.6386607338206</v>
       </c>
       <c r="D40" t="n">
-        <v>-36.3</v>
+        <v>-0.6613392661793966</v>
       </c>
       <c r="E40" t="n">
-        <v>1317.69</v>
+        <v>0.4373696249907029</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>36.8</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>35.81547822064613</v>
       </c>
       <c r="D41" t="n">
-        <v>-36.8</v>
+        <v>-0.9845217793538694</v>
       </c>
       <c r="E41" t="n">
-        <v>1354.24</v>
+        <v>0.9692831340221092</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>37.3</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>36.8833122197145</v>
       </c>
       <c r="D42" t="n">
-        <v>-37.3</v>
+        <v>-0.4166877802854998</v>
       </c>
       <c r="E42" t="n">
-        <v>1391.29</v>
+        <v>0.1736287062392569</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>37.9</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>37.77573340676048</v>
       </c>
       <c r="D43" t="n">
-        <v>-37.9</v>
+        <v>-0.1242665932395184</v>
       </c>
       <c r="E43" t="n">
-        <v>1436.41</v>
+        <v>0.01544218619535592</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>38.5</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>38.52955548243027</v>
       </c>
       <c r="D44" t="n">
-        <v>-38.5</v>
+        <v>0.0295554824302684</v>
       </c>
       <c r="E44" t="n">
-        <v>1482.25</v>
+        <v>0.0008735265416859039</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>38.9</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>39.2027103573383</v>
       </c>
       <c r="D45" t="n">
-        <v>-38.9</v>
+        <v>0.3027103573383059</v>
       </c>
       <c r="E45" t="n">
-        <v>1513.21</v>
+        <v>0.09163356043988483</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>39.4</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>40.11827417529376</v>
       </c>
       <c r="D46" t="n">
-        <v>-39.4</v>
+        <v>0.7182741752937645</v>
       </c>
       <c r="E46" t="n">
-        <v>1552.36</v>
+        <v>0.5159177908939375</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>39.9</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>40.63573555162989</v>
       </c>
       <c r="D47" t="n">
-        <v>-39.9</v>
+        <v>0.7357355516298938</v>
       </c>
       <c r="E47" t="n">
-        <v>1592.01</v>
+        <v>0.5413068019321441</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>40.1</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>39.12693659218619</v>
       </c>
       <c r="D48" t="n">
-        <v>-40.1</v>
+        <v>-0.973063407813811</v>
       </c>
       <c r="E48" t="n">
-        <v>1608.01</v>
+        <v>0.9468523956262269</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>40.6</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>40.86997228496865</v>
       </c>
       <c r="D49" t="n">
-        <v>-40.6</v>
+        <v>0.2699722849686523</v>
       </c>
       <c r="E49" t="n">
-        <v>1648.36</v>
+        <v>0.07288503465119522</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>40.9</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>40.65588761654695</v>
       </c>
       <c r="D50" t="n">
-        <v>-40.9</v>
+        <v>-0.2441123834530501</v>
       </c>
       <c r="E50" t="n">
-        <v>1672.81</v>
+        <v>0.05959085575512896</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>41.2</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>40.29513997690747</v>
       </c>
       <c r="D51" t="n">
-        <v>-41.2</v>
+        <v>-0.9048600230925317</v>
       </c>
       <c r="E51" t="n">
-        <v>1697.44</v>
+        <v>0.818771661391017</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-1665</v>
+        <v>-2.080545998229663</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>56100.876</v>
+        <v>10.74188383000859</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>1122.01752</v>
+        <v>0.2148376766001719</v>
       </c>
     </row>
   </sheetData>

--- a/full/sliding_window_results_window_3.xlsx
+++ b/full/sliding_window_results_window_3.xlsx
@@ -463,13 +463,13 @@
         <v>29.35</v>
       </c>
       <c r="C2" t="n">
-        <v>28.56809871931244</v>
+        <v>28.89450531543122</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.7819012806875634</v>
+        <v>-0.4554946845687766</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6113696127408518</v>
+        <v>0.2074754076704093</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.37</v>
       </c>
       <c r="C3" t="n">
-        <v>28.56090230188462</v>
+        <v>29.03268432587106</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.8090976981153766</v>
+        <v>-0.3373156741289449</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6546390850956011</v>
+        <v>0.1137818640130646</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.54</v>
       </c>
       <c r="C4" t="n">
-        <v>29.40648462030243</v>
+        <v>29.54761987326925</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1335153796975703</v>
+        <v>0.007619873269252508</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01782635661578637</v>
+        <v>5.806246863946891e-05</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.55</v>
       </c>
       <c r="C5" t="n">
-        <v>30.00421754041881</v>
+        <v>29.55194082365931</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4542175404188136</v>
+        <v>0.001940823659310809</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2063135740241165</v>
+        <v>3.766796476540598e-06</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.75</v>
       </c>
       <c r="C6" t="n">
-        <v>30.08550511156546</v>
+        <v>29.6623301892684</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3355051115654604</v>
+        <v>-0.08766981073160451</v>
       </c>
       <c r="E6" t="n">
-        <v>0.112563679886552</v>
+        <v>0.007685995713715358</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>29.84</v>
       </c>
       <c r="C7" t="n">
-        <v>30.13760866815252</v>
+        <v>29.75040369897594</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2976086681525238</v>
+        <v>-0.08959630102405924</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08857091935951907</v>
+        <v>0.008027497157193839</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>29.81</v>
       </c>
       <c r="C8" t="n">
-        <v>30.24145396543597</v>
+        <v>29.82559380003129</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4314539654359741</v>
+        <v>0.01559380003129363</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1861525242904268</v>
+        <v>0.0002431665994159731</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>29.92</v>
       </c>
       <c r="C9" t="n">
-        <v>30.23881880015279</v>
+        <v>30.02450801032186</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3188188001527905</v>
+        <v>0.1045080103218545</v>
       </c>
       <c r="E9" t="n">
-        <v>0.101645427330865</v>
+        <v>0.01092192422143285</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>29.98</v>
       </c>
       <c r="C10" t="n">
-        <v>30.3324748470579</v>
+        <v>29.95178385461215</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3524748470578949</v>
+        <v>-0.028216145387848</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1242385178084864</v>
+        <v>0.000796150860548176</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.04</v>
       </c>
       <c r="C11" t="n">
-        <v>30.15780981532706</v>
+        <v>29.96550515244057</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1178098153270639</v>
+        <v>-0.07449484755942493</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0138791525873969</v>
+        <v>0.005549482312901957</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.21</v>
       </c>
       <c r="C12" t="n">
-        <v>30.00645248447812</v>
+        <v>29.8576357250608</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2035475155218762</v>
+        <v>-0.3523642749391982</v>
       </c>
       <c r="E12" t="n">
-        <v>0.04143159107512844</v>
+        <v>0.1241605822534269</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.22</v>
       </c>
       <c r="C13" t="n">
-        <v>30.11347628287443</v>
+        <v>29.86505841657388</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1065237171255689</v>
+        <v>-0.3549415834261183</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01134730231024821</v>
+        <v>0.1259835276450401</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.38</v>
       </c>
       <c r="C14" t="n">
-        <v>29.99755940397955</v>
+        <v>29.93791584109502</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.382440596020448</v>
+        <v>-0.4420841589049793</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1462608094844755</v>
+        <v>0.195438403554723</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.44</v>
       </c>
       <c r="C15" t="n">
-        <v>30.02760648670544</v>
+        <v>30.00603362932825</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.412393513294564</v>
+        <v>-0.4339663706717545</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1700684098074337</v>
+        <v>0.1883268108740146</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.48</v>
       </c>
       <c r="C16" t="n">
-        <v>30.198318076291</v>
+        <v>30.28668385931438</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2816819237090051</v>
+        <v>-0.1933161406856208</v>
       </c>
       <c r="E16" t="n">
-        <v>0.07934470614440579</v>
+        <v>0.03737113024958272</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>30.69</v>
       </c>
       <c r="C17" t="n">
-        <v>30.46317541374856</v>
+        <v>30.59291630416837</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2268245862514426</v>
+        <v>-0.09708369583162835</v>
       </c>
       <c r="E17" t="n">
-        <v>0.05144939292813814</v>
+        <v>0.009425243996328131</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>30.75</v>
       </c>
       <c r="C18" t="n">
-        <v>30.7874844356307</v>
+        <v>30.24224503559068</v>
       </c>
       <c r="D18" t="n">
-        <v>0.03748443563070225</v>
+        <v>-0.5077549644093189</v>
       </c>
       <c r="E18" t="n">
-        <v>0.001405082914552261</v>
+        <v>0.2578151038823087</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>30.94</v>
       </c>
       <c r="C19" t="n">
-        <v>31.48652885860169</v>
+        <v>30.91328848534648</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5465288586016932</v>
+        <v>-0.02671151465351684</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2986937932844695</v>
+        <v>0.0007135050150850451</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>30.95</v>
       </c>
       <c r="C20" t="n">
-        <v>31.39704363937706</v>
+        <v>30.93196381555407</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4470436393770605</v>
+        <v>-0.01803618444592914</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1998480155074873</v>
+        <v>0.0003253039493675761</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.02</v>
       </c>
       <c r="C21" t="n">
-        <v>31.22176637042529</v>
+        <v>30.98172383125704</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2017663704252861</v>
+        <v>-0.03827616874296069</v>
       </c>
       <c r="E21" t="n">
-        <v>0.04070966823459377</v>
+        <v>0.001465065093639601</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.12</v>
       </c>
       <c r="C22" t="n">
-        <v>31.20880547241887</v>
+        <v>31.16988054481348</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08880547241886561</v>
+        <v>0.04988054481348314</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0078864119315379</v>
+        <v>0.0024880687508899</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.28</v>
       </c>
       <c r="C23" t="n">
-        <v>31.71783149681082</v>
+        <v>31.41007720012863</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4378314968108157</v>
+        <v>0.1300772001286319</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1916964195995993</v>
+        <v>0.01692007799330415</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>31.38</v>
       </c>
       <c r="C24" t="n">
-        <v>31.67425022380877</v>
+        <v>31.57459527955494</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2942502238087705</v>
+        <v>0.1945952795549388</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08658319421151155</v>
+        <v>0.0378673228250648</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>31.58</v>
       </c>
       <c r="C25" t="n">
-        <v>31.80670018641877</v>
+        <v>31.75618732948094</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2267001864187677</v>
+        <v>0.1761873294809426</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05139297452230401</v>
+        <v>0.03104197506962623</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>31.65</v>
       </c>
       <c r="C26" t="n">
-        <v>31.57236529702934</v>
+        <v>31.51604409642252</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.07763470297066277</v>
+        <v>-0.1339559035774833</v>
       </c>
       <c r="E26" t="n">
-        <v>0.006027147105343035</v>
+        <v>0.01794418410326001</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>31.88</v>
       </c>
       <c r="C27" t="n">
-        <v>31.80795770925392</v>
+        <v>31.74178921358584</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.07204229074607937</v>
+        <v>-0.1382107864141595</v>
       </c>
       <c r="E27" t="n">
-        <v>0.005190091655942634</v>
+        <v>0.01910222148122042</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>32.28</v>
       </c>
       <c r="C28" t="n">
-        <v>32.40764967107331</v>
+        <v>31.98964366519843</v>
       </c>
       <c r="D28" t="n">
-        <v>0.127649671073307</v>
+        <v>-0.2903563348015723</v>
       </c>
       <c r="E28" t="n">
-        <v>0.01629443852512348</v>
+        <v>0.08430680115940274</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>32.45</v>
       </c>
       <c r="C29" t="n">
-        <v>32.0779747708137</v>
+        <v>32.03946202702225</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3720252291863062</v>
+        <v>-0.4105379729777496</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1384027711511236</v>
+        <v>0.1685414272566795</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>32.85</v>
       </c>
       <c r="C30" t="n">
-        <v>33.49615976197383</v>
+        <v>33.09529717026919</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6461597619738271</v>
+        <v>0.2452971702691897</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4175224379940728</v>
+        <v>0.06017070174207186</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>32.9</v>
       </c>
       <c r="C31" t="n">
-        <v>32.90623986695228</v>
+        <v>32.76727725085725</v>
       </c>
       <c r="D31" t="n">
-        <v>0.006239866952284956</v>
+        <v>-0.1327227491427436</v>
       </c>
       <c r="E31" t="n">
-        <v>3.893593958221794e-05</v>
+        <v>0.01761532814000765</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>33.1</v>
       </c>
       <c r="C32" t="n">
-        <v>33.22022286182911</v>
+        <v>33.18462893582871</v>
       </c>
       <c r="D32" t="n">
-        <v>0.120222861829113</v>
+        <v>0.08462893582870379</v>
       </c>
       <c r="E32" t="n">
-        <v>0.014453536506382</v>
+        <v>0.007162056779498864</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>33.4</v>
       </c>
       <c r="C33" t="n">
-        <v>33.03518120681197</v>
+        <v>33.16734865370236</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.3648187931880287</v>
+        <v>-0.2326513462976365</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1330927518631696</v>
+        <v>0.05412664893410279</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>33.7</v>
       </c>
       <c r="C34" t="n">
-        <v>33.75397210975283</v>
+        <v>33.73945918166745</v>
       </c>
       <c r="D34" t="n">
-        <v>0.05397210975282718</v>
+        <v>0.03945918166744633</v>
       </c>
       <c r="E34" t="n">
-        <v>0.002912988631171223</v>
+        <v>0.001557027017864533</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>34.1</v>
       </c>
       <c r="C35" t="n">
-        <v>34.66480062472593</v>
+        <v>34.43369396526402</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5648006247259261</v>
+        <v>0.3336939652640183</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3189997456907964</v>
+        <v>0.1113516624536239</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>34.4</v>
       </c>
       <c r="C36" t="n">
-        <v>34.41753274239829</v>
+        <v>34.47303632894979</v>
       </c>
       <c r="D36" t="n">
-        <v>0.01753274239828784</v>
+        <v>0.07303632894979017</v>
       </c>
       <c r="E36" t="n">
-        <v>0.00030739705600472</v>
+        <v>0.005334305346461958</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>34.9</v>
       </c>
       <c r="C37" t="n">
-        <v>34.92800287556167</v>
+        <v>34.96818273016046</v>
       </c>
       <c r="D37" t="n">
-        <v>0.02800287556166836</v>
+        <v>0.0681827301604585</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0007841610397222831</v>
+        <v>0.004648884692133898</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>35.3</v>
       </c>
       <c r="C38" t="n">
-        <v>34.47907648458726</v>
+        <v>34.61693598698782</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.820923515412737</v>
+        <v>-0.6830640130121779</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6739154181576062</v>
+        <v>0.4665764458723007</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>35.7</v>
       </c>
       <c r="C39" t="n">
-        <v>34.76454817958464</v>
+        <v>35.11379662293022</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9354518204153663</v>
+        <v>-0.5862033770697863</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8750701083184228</v>
+        <v>0.3436343992880221</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>36.3</v>
       </c>
       <c r="C40" t="n">
-        <v>35.6386607338206</v>
+        <v>36.03713499096578</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.6613392661793966</v>
+        <v>-0.2628650090342219</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4373696249907029</v>
+        <v>0.06909801297456158</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>36.8</v>
       </c>
       <c r="C41" t="n">
-        <v>35.81547822064613</v>
+        <v>36.39176960655069</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.9845217793538694</v>
+        <v>-0.4082303934493083</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9692831340221092</v>
+        <v>0.1666520541357771</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>37.3</v>
       </c>
       <c r="C42" t="n">
-        <v>36.8833122197145</v>
+        <v>37.3130945217657</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4166877802854998</v>
+        <v>0.01309452176570147</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1736287062392569</v>
+        <v>0.0001714665002724296</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>37.9</v>
       </c>
       <c r="C43" t="n">
-        <v>37.77573340676048</v>
+        <v>37.86991214028122</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1242665932395184</v>
+        <v>-0.03008785971877614</v>
       </c>
       <c r="E43" t="n">
-        <v>0.01544218619535592</v>
+        <v>0.0009052793024567521</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>38.5</v>
       </c>
       <c r="C44" t="n">
-        <v>38.52955548243027</v>
+        <v>38.23213883000086</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0295554824302684</v>
+        <v>-0.2678611699991365</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0008735265416859039</v>
+        <v>0.07174960639330628</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>38.9</v>
       </c>
       <c r="C45" t="n">
-        <v>39.2027103573383</v>
+        <v>38.81992058684555</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3027103573383059</v>
+        <v>-0.08007941315445066</v>
       </c>
       <c r="E45" t="n">
-        <v>0.09163356043988483</v>
+        <v>0.006412712411161206</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>39.4</v>
       </c>
       <c r="C46" t="n">
-        <v>40.11827417529376</v>
+        <v>39.29652412414337</v>
       </c>
       <c r="D46" t="n">
-        <v>0.7182741752937645</v>
+        <v>-0.1034758758566241</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5159177908939375</v>
+        <v>0.01070725688429548</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>39.9</v>
       </c>
       <c r="C47" t="n">
-        <v>40.63573555162989</v>
+        <v>39.77329815586963</v>
       </c>
       <c r="D47" t="n">
-        <v>0.7357355516298938</v>
+        <v>-0.1267018441303662</v>
       </c>
       <c r="E47" t="n">
-        <v>0.5413068019321441</v>
+        <v>0.01605335730603562</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>40.1</v>
       </c>
       <c r="C48" t="n">
-        <v>39.12693659218619</v>
+        <v>39.80730337313249</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.973063407813811</v>
+        <v>-0.2926966268675102</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9468523956262269</v>
+        <v>0.08567131537961849</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>40.6</v>
       </c>
       <c r="C49" t="n">
-        <v>40.86997228496865</v>
+        <v>40.41073223755519</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2699722849686523</v>
+        <v>-0.189267762444814</v>
       </c>
       <c r="E49" t="n">
-        <v>0.07288503465119522</v>
+        <v>0.03582228590086656</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>40.9</v>
       </c>
       <c r="C50" t="n">
-        <v>40.65588761654695</v>
+        <v>40.98844965860037</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.2441123834530501</v>
+        <v>0.0884496586003749</v>
       </c>
       <c r="E50" t="n">
-        <v>0.05959085575512896</v>
+        <v>0.007823342106522874</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>41.2</v>
       </c>
       <c r="C51" t="n">
-        <v>40.29513997690747</v>
+        <v>40.7757119380915</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.9048600230925317</v>
+        <v>-0.4242880619084985</v>
       </c>
       <c r="E51" t="n">
-        <v>0.818771661391017</v>
+        <v>0.1800203594780699</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-2.080545998229663</v>
+        <v>-6.704333666203308</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>10.74188383000859</v>
+        <v>3.397044582005794</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.2148376766001719</v>
+        <v>0.06794089164011589</v>
       </c>
     </row>
   </sheetData>
